--- a/ExcelMaster/Sample/Assets/Excels/Item.xlsx
+++ b/ExcelMaster/Sample/Assets/Excels/Item.xlsx
@@ -8,24 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaga\Documents\UnityProjects\ExcelMaster\ExcelMaster\Sample\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD7EC52-27D5-4103-B710-1378C6EBFB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B68BD7-83DF-4BF7-A910-60AB256B1DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Item" sheetId="1" r:id="rId1"/>
+    <sheet name="WorkbookConfig" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -143,11 +153,51 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NameSpace:Confront</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ClassName: Item</t>
+    <t>WorkbookConfig</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SheetName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ClassName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Namespace</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BinaryName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ModularPulse.Master</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>item.bytes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CodeOutputDirectory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BinaryOutputDirectory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/Scripts/Generated</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/StreamingAssets/Master</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -473,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.25" bestFit="1" customWidth="1"/>
@@ -491,148 +541,140 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="E5">
+        <v>55</v>
+      </c>
+      <c r="F5">
+        <v>66</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
         <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>55</v>
-      </c>
-      <c r="F6">
-        <v>66</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -640,4 +682,73 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCD1EB7-0E30-42A9-8930-66F982C3B0D7}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelMaster/Sample/Assets/Excels/Item.xlsx
+++ b/ExcelMaster/Sample/Assets/Excels/Item.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaga\Documents\UnityProjects\ExcelMaster\ExcelMaster\Sample\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B68BD7-83DF-4BF7-A910-60AB256B1DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07792310-9D53-4F29-8B69-6ED0CB06E937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
     <sheet name="WorkbookConfig" sheetId="2" r:id="rId2"/>
+    <sheet name="ItemParams" sheetId="3" r:id="rId3"/>
+    <sheet name="ItemPramsConfig" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -105,10 +107,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>enum</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Goo</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -198,6 +196,46 @@
   </si>
   <si>
     <t>Assets/StreamingAssets/Master</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>System.Data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AdditionalUsings</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>System.Diagnostics</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TableName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enum:EnumSample</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enum:HandType</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enum:ItemCategory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ItemParams</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BuilderOutputDirectory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Assets/Editor/Generated</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -535,8 +573,9 @@
     <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -562,15 +601,15 @@
         <v>16</v>
       </c>
       <c r="M1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -588,13 +627,13 @@
         <v>11</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -617,13 +656,13 @@
         <v>8</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -640,13 +679,13 @@
         <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -669,13 +708,13 @@
         <v>66</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -686,64 +725,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FCD1EB7-0E30-42A9-8930-66F982C3B0D7}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
         <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -751,4 +809,166 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A920C1FA-8C6D-46CD-AE7C-7685BF63BAC2}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="15.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A6E2B2-EF52-48B2-A2B0-E9A22C59AF5B}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>